--- a/data/trans_dic/P37A$otros-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P37A$otros-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,12</t>
+          <t>0,37; 2,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,17 +742,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,0; 1,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 1,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,61</t>
+          <t>0,72; 2,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,93</t>
+          <t>0,0; 1,05</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,03</t>
+          <t>0,76; 2,08</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,07</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -867,22 +867,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,07</t>
+          <t>0,0; 1,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,89</t>
+          <t>0,55; 2,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,75</t>
+          <t>0,0; 1,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,78</t>
+          <t>0,0; 2,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,27 +892,27 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,04; 1,07</t>
+          <t>0,13; 1,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,01</t>
+          <t>0,1; 1,02</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,91</t>
+          <t>0,0; 0,82</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,79</t>
+          <t>0,0; 0,81</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,81</t>
+          <t>0,48; 1,83</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,99</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 1,77</t>
+          <t>0,4; 2,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1027,32 +1027,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,44</t>
+          <t>0,0; 4,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 2,77</t>
+          <t>0,33; 3,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,99</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,54</t>
+          <t>0,0; 0,44</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,28</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,61</t>
+          <t>0,53; 2,28</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,5</t>
+          <t>0,0; 0,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,87</t>
+          <t>0,07; 0,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,51</t>
+          <t>0,24; 1,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,17 +1162,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,67</t>
+          <t>0,0; 0,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,87</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,65</t>
+          <t>0,5; 1,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,32</t>
+          <t>0,0; 0,36</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,69</t>
+          <t>0,09; 0,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,33</t>
+          <t>0,48; 1,36</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -1287,24 +1287,24 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>0,0; 0,85</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0,19; 1,71</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 1,15</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,86</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0,21; 1,96</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,25</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,62</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
           <t>0,13; 1,05</t>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,6</t>
+          <t>0,56; 1,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,72</t>
+          <t>0,0; 0,9</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1327,19 +1327,19 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,71</t>
+          <t>0,07; 0,73</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,56</t>
+          <t>0,52; 1,41</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,07</t>
+          <t>0,55; 4,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1437,42 +1437,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,4</t>
+          <t>0,0; 0,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,46</t>
+          <t>0,0; 0,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,04</t>
+          <t>0,09; 1,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,56</t>
+          <t>0,45; 2,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,32</t>
+          <t>0,0; 0,33</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,4</t>
+          <t>0,0; 0,37</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,35</t>
+          <t>0,3; 1,28</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,97</t>
+          <t>0,34; 1,78</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,27</t>
+          <t>0,03; 0,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,66</t>
+          <t>0,19; 0,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,18</t>
+          <t>0,57; 1,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1582,37 +1582,37 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,34</t>
+          <t>0,05; 0,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,58</t>
+          <t>0,18; 0,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,39</t>
+          <t>0,73; 1,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,23</t>
+          <t>0,05; 0,22</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,21</t>
+          <t>0,05; 0,21</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,53</t>
+          <t>0,2; 0,51</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,15</t>
+          <t>0,74; 1,19</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4825</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6725</t>
+          <t>6951</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11550</t>
+          <t>12752</t>
         </is>
       </c>
     </row>
@@ -1937,12 +1937,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6997</t>
+          <t>0; 8932</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1765; 10715</t>
+          <t>2061; 12229</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1952,17 +1952,17 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4678</t>
+          <t>0; 4707</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4449</t>
+          <t>0; 4495</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3238; 11673</t>
+          <t>3506; 13327</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1972,17 +1972,17 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 4667</t>
+          <t>0; 4677</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 7243</t>
+          <t>0; 8129</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6408; 19325</t>
+          <t>7906; 21650</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>6800</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7669</t>
+          <t>8697</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3921</t>
+          <t>0; 4356</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2145,22 +2145,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 7807</t>
+          <t>0; 5701</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2325; 13078</t>
+          <t>2646; 14090</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6515</t>
+          <t>0; 5762</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6019</t>
+          <t>0; 7484</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2170,27 +2170,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>160; 4106</t>
+          <t>556; 5051</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>766; 7438</t>
+          <t>767; 7510</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 6921</t>
+          <t>0; 6231</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5886</t>
+          <t>0; 6050</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3561; 15151</t>
+          <t>4325; 16575</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4706</t>
+          <t>5731</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>7850</t>
         </is>
       </c>
     </row>
@@ -2343,12 +2343,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5346</t>
+          <t>0; 6153</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4820</t>
+          <t>0; 4824</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>309; 11809</t>
+          <t>1884; 12654</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2373,32 +2373,32 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 7381</t>
+          <t>0; 7309</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>166; 4622</t>
+          <t>614; 5998</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 7037</t>
+          <t>0; 6123</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 4834</t>
+          <t>0; 3922</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 9707</t>
+          <t>0; 8775</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1473; 13444</t>
+          <t>3493; 15012</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7425</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8188</t>
+          <t>8372</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15614</t>
+          <t>16030</t>
         </is>
       </c>
     </row>
@@ -2551,22 +2551,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6212</t>
+          <t>0; 6898</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4819</t>
+          <t>0; 4826</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>792; 10005</t>
+          <t>789; 10107</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2884; 15633</t>
+          <t>2765; 16517</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2576,37 +2576,37 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5145</t>
+          <t>0; 5235</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 7172</t>
+          <t>0; 7134</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3423; 16137</t>
+          <t>4301; 16376</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5207</t>
+          <t>0; 5240</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 6146</t>
+          <t>0; 6860</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2040; 13551</t>
+          <t>1792; 12825</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8428; 26767</t>
+          <t>9468; 27058</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7688</t>
+          <t>8323</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11479</t>
+          <t>12280</t>
         </is>
       </c>
     </row>
@@ -2769,59 +2769,59 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5325</t>
+          <t>0; 5306</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>983; 9325</t>
+          <t>1094; 9687</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 7117</t>
+          <t>0; 6552</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4752</t>
+          <t>0; 6526</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>924; 7762</t>
+          <t>925; 7759</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3834; 13478</t>
+          <t>4657; 14561</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 6633</t>
+          <t>0; 8259</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 5876</t>
+          <t>0; 5875</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1000; 9616</t>
+          <t>999; 9950</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6999; 20513</t>
+          <t>7325; 19719</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>8897</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8897</t>
+          <t>8829</t>
         </is>
       </c>
     </row>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1098; 11700</t>
+          <t>1579; 11749</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2987,42 +2987,42 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4955</t>
+          <t>0; 3993</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5075</t>
+          <t>0; 5613</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>936; 11210</t>
+          <t>1015; 11190</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3909; 19461</t>
+          <t>3762; 19349</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 4957</t>
+          <t>0; 5155</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 5469</t>
+          <t>0; 5086</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4582; 18487</t>
+          <t>4100; 17513</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3955; 19783</t>
+          <t>3689; 19275</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27090</t>
+          <t>29947</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>34233</t>
+          <t>36491</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>61324</t>
+          <t>66438</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>876; 8864</t>
+          <t>877; 9090</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 6906</t>
+          <t>0; 6781</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6436; 22435</t>
+          <t>6582; 22079</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17391; 39720</t>
+          <t>19730; 41883</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>991; 10066</t>
+          <t>989; 10013</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1956; 12237</t>
+          <t>1944; 12276</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6017; 20564</t>
+          <t>6326; 21209</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>24077; 49654</t>
+          <t>26547; 49860</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3599; 15571</t>
+          <t>3511; 14772</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2999; 14734</t>
+          <t>3148; 14892</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15456; 36437</t>
+          <t>14031; 35530</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>47102; 80227</t>
+          <t>52433; 84363</t>
         </is>
       </c>
     </row>
